--- a/pfas-tracker.xlsx
+++ b/pfas-tracker.xlsx
@@ -548,7 +548,7 @@
       <c r="C3" s="3" t="inlineStr"/>
       <c r="D3" s="3" t="inlineStr"/>
       <c r="E3" s="3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
@@ -614,7 +614,7 @@
       <c r="C6" s="3" t="inlineStr"/>
       <c r="D6" s="3" t="inlineStr"/>
       <c r="E6" s="3" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
@@ -636,7 +636,7 @@
       <c r="C7" s="3" t="inlineStr"/>
       <c r="D7" s="3" t="inlineStr"/>
       <c r="E7" s="3" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
@@ -658,7 +658,7 @@
       <c r="C8" s="3" t="inlineStr"/>
       <c r="D8" s="3" t="inlineStr"/>
       <c r="E8" s="3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
@@ -680,7 +680,7 @@
       <c r="C9" s="3" t="inlineStr"/>
       <c r="D9" s="3" t="inlineStr"/>
       <c r="E9" s="3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
@@ -724,7 +724,7 @@
       <c r="C11" s="3" t="inlineStr"/>
       <c r="D11" s="3" t="inlineStr"/>
       <c r="E11" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
@@ -768,7 +768,7 @@
       <c r="C13" s="3" t="inlineStr"/>
       <c r="D13" s="3" t="inlineStr"/>
       <c r="E13" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
       <c r="C14" s="3" t="inlineStr"/>
       <c r="D14" s="3" t="inlineStr"/>
       <c r="E14" s="3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
@@ -922,7 +922,7 @@
       <c r="C20" s="3" t="inlineStr"/>
       <c r="D20" s="3" t="inlineStr"/>
       <c r="E20" s="3" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
@@ -966,7 +966,7 @@
       <c r="C22" s="3" t="inlineStr"/>
       <c r="D22" s="3" t="inlineStr"/>
       <c r="E22" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
@@ -988,7 +988,7 @@
       <c r="C23" s="3" t="inlineStr"/>
       <c r="D23" s="3" t="inlineStr"/>
       <c r="E23" s="3" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
@@ -1010,7 +1010,7 @@
       <c r="C24" s="3" t="inlineStr"/>
       <c r="D24" s="3" t="inlineStr"/>
       <c r="E24" s="3" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
@@ -1054,7 +1054,7 @@
       <c r="C26" s="3" t="inlineStr"/>
       <c r="D26" s="3" t="inlineStr"/>
       <c r="E26" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
@@ -1076,7 +1076,7 @@
       <c r="C27" s="3" t="inlineStr"/>
       <c r="D27" s="3" t="inlineStr"/>
       <c r="E27" s="3" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
@@ -1120,7 +1120,7 @@
       <c r="C29" s="3" t="inlineStr"/>
       <c r="D29" s="3" t="inlineStr"/>
       <c r="E29" s="3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
@@ -1164,7 +1164,7 @@
       <c r="C31" s="3" t="inlineStr"/>
       <c r="D31" s="3" t="inlineStr"/>
       <c r="E31" s="3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
@@ -1186,7 +1186,7 @@
       <c r="C32" s="3" t="inlineStr"/>
       <c r="D32" s="3" t="inlineStr"/>
       <c r="E32" s="3" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
@@ -1208,7 +1208,7 @@
       <c r="C33" s="3" t="inlineStr"/>
       <c r="D33" s="3" t="inlineStr"/>
       <c r="E33" s="3" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
@@ -1318,7 +1318,7 @@
       <c r="C38" s="3" t="inlineStr"/>
       <c r="D38" s="3" t="inlineStr"/>
       <c r="E38" s="3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
@@ -1340,7 +1340,7 @@
       <c r="C39" s="3" t="inlineStr"/>
       <c r="D39" s="3" t="inlineStr"/>
       <c r="E39" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
@@ -1362,7 +1362,7 @@
       <c r="C40" s="3" t="inlineStr"/>
       <c r="D40" s="3" t="inlineStr"/>
       <c r="E40" s="3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F40" s="4" t="inlineStr">
         <is>
@@ -1384,7 +1384,7 @@
       <c r="C41" s="3" t="inlineStr"/>
       <c r="D41" s="3" t="inlineStr"/>
       <c r="E41" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
@@ -1428,7 +1428,7 @@
       <c r="C43" s="3" t="inlineStr"/>
       <c r="D43" s="3" t="inlineStr"/>
       <c r="E43" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F43" s="4" t="inlineStr">
         <is>
@@ -1494,7 +1494,7 @@
       <c r="C46" s="3" t="inlineStr"/>
       <c r="D46" s="3" t="inlineStr"/>
       <c r="E46" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F46" s="4" t="inlineStr">
         <is>
@@ -1516,7 +1516,7 @@
       <c r="C47" s="3" t="inlineStr"/>
       <c r="D47" s="3" t="inlineStr"/>
       <c r="E47" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F47" s="4" t="inlineStr">
         <is>
@@ -1538,7 +1538,7 @@
       <c r="C48" s="3" t="inlineStr"/>
       <c r="D48" s="3" t="inlineStr"/>
       <c r="E48" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F48" s="4" t="inlineStr">
         <is>
@@ -1560,7 +1560,7 @@
       <c r="C49" s="3" t="inlineStr"/>
       <c r="D49" s="3" t="inlineStr"/>
       <c r="E49" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F49" s="4" t="inlineStr">
         <is>
@@ -1582,7 +1582,7 @@
       <c r="C50" s="3" t="inlineStr"/>
       <c r="D50" s="3" t="inlineStr"/>
       <c r="E50" s="3" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="F50" s="4" t="inlineStr">
         <is>
@@ -1604,7 +1604,7 @@
       <c r="C51" s="3" t="inlineStr"/>
       <c r="D51" s="3" t="inlineStr"/>
       <c r="E51" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F51" s="4" t="inlineStr">
         <is>

--- a/pfas-tracker.xlsx
+++ b/pfas-tracker.xlsx
@@ -614,7 +614,7 @@
       <c r="C6" s="3" t="inlineStr"/>
       <c r="D6" s="3" t="inlineStr"/>
       <c r="E6" s="3" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
       <c r="C14" s="3" t="inlineStr"/>
       <c r="D14" s="3" t="inlineStr"/>
       <c r="E14" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
@@ -922,7 +922,7 @@
       <c r="C20" s="3" t="inlineStr"/>
       <c r="D20" s="3" t="inlineStr"/>
       <c r="E20" s="3" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
@@ -1186,7 +1186,7 @@
       <c r="C32" s="3" t="inlineStr"/>
       <c r="D32" s="3" t="inlineStr"/>
       <c r="E32" s="3" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
